--- a/Bases/Confirmados Asamblea Rural 24 Oct.xlsx
+++ b/Bases/Confirmados Asamblea Rural 24 Oct.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dannamoralesbeltran/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCEA689-5B33-1E4F-8900-FD6AF8A7BDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BF9180-7771-6648-A0E8-9821071EF554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17020" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consolidado" sheetId="5" state="hidden" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="465">
   <si>
     <t>IDPAC</t>
   </si>
@@ -580,9 +580,6 @@
     <t>dsgonzalez08@ucatolica.edu.co</t>
   </si>
   <si>
-    <t>Hilary Oriana Camacho Gonzalez</t>
-  </si>
-  <si>
     <t>No tenemos forma de verificar este caso. No incluye correo o número de contacto.</t>
   </si>
   <si>
@@ -611,9 +608,6 @@
   </si>
   <si>
     <t>No contesto, se le envio correo con la información.</t>
-  </si>
-  <si>
-    <t>María Camila Marín Gualtero</t>
   </si>
   <si>
     <t>No tiene numero celular</t>
@@ -951,9 +945,6 @@
   </si>
   <si>
     <t>Machadohaidtheryeff@gmail.com</t>
-  </si>
-  <si>
-    <t>Sin información</t>
   </si>
   <si>
     <t>3014748856 - Karen Gutiérrez (Mamá)</t>
@@ -1986,6 +1977,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2000,30 +2015,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12063,10 +12054,10 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>5</v>
@@ -12180,13 +12171,13 @@
         <v>0</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F4" s="22">
         <v>1140918777</v>
@@ -12202,7 +12193,7 @@
       </c>
       <c r="L4" s="17"/>
       <c r="M4" s="17" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -12353,13 +12344,13 @@
         <v>0</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F9" s="22">
         <v>1006877782</v>
@@ -12375,7 +12366,7 @@
       </c>
       <c r="L9" s="17"/>
       <c r="M9" s="17" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -12386,13 +12377,13 @@
         <v>0</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F10" s="22">
         <v>1022941390</v>
@@ -12408,7 +12399,7 @@
       </c>
       <c r="L10" s="17"/>
       <c r="M10" s="17" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -12454,13 +12445,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="21"/>
@@ -12470,24 +12461,24 @@
       <c r="K12" s="10"/>
       <c r="L12" s="17"/>
       <c r="M12" s="17" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="76">
+      <c r="A13" s="70">
         <v>10</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F13" s="22">
         <v>1028783625</v>
@@ -12503,129 +12494,129 @@
       </c>
       <c r="L13" s="17"/>
       <c r="M13" s="17" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="72">
+      <c r="A14" s="66">
         <v>15</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>450</v>
-      </c>
-      <c r="E14" s="72" t="s">
-        <v>466</v>
-      </c>
-      <c r="F14" s="73"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="72"/>
+        <v>447</v>
+      </c>
+      <c r="E14" s="66" t="s">
+        <v>463</v>
+      </c>
+      <c r="F14" s="67"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="66"/>
       <c r="M14" s="17" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="72">
+      <c r="A15" s="66">
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>450</v>
-      </c>
-      <c r="E15" s="77" t="s">
+        <v>447</v>
+      </c>
+      <c r="E15" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="F15" s="78">
+      <c r="F15" s="72">
         <v>1140917549</v>
       </c>
-      <c r="G15" s="74">
+      <c r="G15" s="68">
         <v>3235104254</v>
       </c>
-      <c r="H15" s="77" t="s">
+      <c r="H15" s="71" t="s">
         <v>119</v>
       </c>
-      <c r="I15" s="77" t="s">
+      <c r="I15" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="77"/>
-      <c r="K15" s="78" t="s">
+      <c r="J15" s="71"/>
+      <c r="K15" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="L15" s="78"/>
-      <c r="M15" s="79"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="73"/>
     </row>
     <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="72">
+      <c r="A16" s="66">
         <v>13</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="E16" s="66" t="s">
+        <v>448</v>
+      </c>
+      <c r="F16" s="67">
+        <v>1023031689</v>
+      </c>
+      <c r="G16" s="68" t="s">
         <v>449</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="H16" s="66" t="s">
         <v>450</v>
       </c>
-      <c r="E16" s="72" t="s">
-        <v>451</v>
-      </c>
-      <c r="F16" s="73">
-        <v>1023031689</v>
-      </c>
-      <c r="G16" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="H16" s="72" t="s">
-        <v>453</v>
-      </c>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="78" t="s">
+      <c r="I16" s="66"/>
+      <c r="J16" s="66"/>
+      <c r="K16" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
+      <c r="L16" s="66"/>
+      <c r="M16" s="66"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="72">
+      <c r="A17" s="66">
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>450</v>
-      </c>
-      <c r="E17" s="72" t="s">
-        <v>180</v>
-      </c>
-      <c r="F17" s="73"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="75"/>
-      <c r="L17" s="72"/>
+        <v>447</v>
+      </c>
+      <c r="E17" s="66" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" s="67"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="66"/>
       <c r="M17" s="17" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
@@ -15804,7 +15795,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E6" s="46">
         <v>80040922</v>
@@ -15819,7 +15810,7 @@
       </c>
       <c r="L6" s="46"/>
       <c r="M6" s="47" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="N6" s="37"/>
     </row>
@@ -15834,7 +15825,7 @@
         <v>21</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E7" s="46">
         <v>1003479565</v>
@@ -15849,7 +15840,7 @@
       </c>
       <c r="L7" s="46"/>
       <c r="M7" s="49" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="N7" s="37"/>
     </row>
@@ -19263,10 +19254,10 @@
         <v>21</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>24</v>
@@ -19281,7 +19272,7 @@
       <c r="J2" s="26"/>
       <c r="K2" s="25"/>
       <c r="L2" s="27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19295,16 +19286,16 @@
         <v>21</v>
       </c>
       <c r="D3" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>362</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>363</v>
+      </c>
+      <c r="G3" s="27" t="s">
         <v>364</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>365</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>366</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>367</v>
       </c>
       <c r="H3" s="27" t="s">
         <v>25</v>
@@ -19315,7 +19306,7 @@
       </c>
       <c r="K3" s="27"/>
       <c r="L3" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19329,16 +19320,16 @@
         <v>21</v>
       </c>
       <c r="D4" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="G4" s="27" t="s">
         <v>380</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>381</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>382</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>383</v>
       </c>
       <c r="H4" s="27" t="s">
         <v>25</v>
@@ -19349,7 +19340,7 @@
       </c>
       <c r="K4" s="27"/>
       <c r="L4" s="27" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19363,16 +19354,16 @@
         <v>21</v>
       </c>
       <c r="D5" s="27" t="s">
+        <v>370</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="G5" s="27" t="s">
         <v>373</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>374</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>375</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>376</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>25</v>
@@ -19383,7 +19374,7 @@
       </c>
       <c r="K5" s="27"/>
       <c r="L5" s="27" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19397,7 +19388,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E6" s="22">
         <v>1000351200</v>
@@ -19406,7 +19397,7 @@
         <v>3026580366</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H6" s="22" t="s">
         <v>25</v>
@@ -19431,16 +19422,16 @@
         <v>21</v>
       </c>
       <c r="D7" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="G7" s="27" t="s">
         <v>387</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>389</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>390</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>48</v>
@@ -19455,7 +19446,7 @@
         <v>3227140983</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19469,10 +19460,10 @@
         <v>21</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F8" s="25">
         <v>3157973841</v>
@@ -19489,7 +19480,7 @@
       </c>
       <c r="K8" s="25"/>
       <c r="L8" s="27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19503,16 +19494,16 @@
         <v>21</v>
       </c>
       <c r="D9" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>395</v>
+      </c>
+      <c r="G9" s="27" t="s">
         <v>396</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>397</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>398</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>399</v>
       </c>
       <c r="H9" s="27" t="s">
         <v>25</v>
@@ -19523,7 +19514,7 @@
       </c>
       <c r="K9" s="27"/>
       <c r="L9" s="27" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19537,16 +19528,16 @@
         <v>21</v>
       </c>
       <c r="D10" s="27" t="s">
+        <v>398</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>400</v>
+      </c>
+      <c r="G10" s="27" t="s">
         <v>401</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>402</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>403</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>404</v>
       </c>
       <c r="H10" s="27" t="s">
         <v>25</v>
@@ -19557,7 +19548,7 @@
       </c>
       <c r="K10" s="27"/>
       <c r="L10" s="27" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19571,10 +19562,10 @@
         <v>21</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F11" s="25" t="s">
         <v>24</v>
@@ -19589,7 +19580,7 @@
       <c r="J11" s="26"/>
       <c r="K11" s="25"/>
       <c r="L11" s="27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19603,16 +19594,16 @@
         <v>21</v>
       </c>
       <c r="D12" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>406</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="G12" s="27" t="s">
         <v>408</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>409</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>410</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>411</v>
       </c>
       <c r="H12" s="27" t="s">
         <v>48</v>
@@ -19622,10 +19613,10 @@
       </c>
       <c r="J12" s="28"/>
       <c r="K12" s="27" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="L12" s="27" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19639,7 +19630,7 @@
         <v>21</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E13" s="27">
         <v>1030554041</v>
@@ -19651,7 +19642,7 @@
       <c r="J13" s="28"/>
       <c r="K13" s="27"/>
       <c r="L13" s="27" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19665,16 +19656,16 @@
         <v>21</v>
       </c>
       <c r="D14" s="27" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>412</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="G14" s="27" t="s">
         <v>414</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>415</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>416</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>417</v>
       </c>
       <c r="H14" s="27" t="s">
         <v>25</v>
@@ -19683,7 +19674,7 @@
       <c r="J14" s="28"/>
       <c r="K14" s="27"/>
       <c r="L14" s="27" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19697,16 +19688,16 @@
         <v>21</v>
       </c>
       <c r="D15" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>417</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="G15" s="27" t="s">
         <v>419</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>420</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>421</v>
-      </c>
-      <c r="G15" s="27" t="s">
-        <v>422</v>
       </c>
       <c r="H15" s="27" t="s">
         <v>25</v>
@@ -19715,7 +19706,7 @@
       <c r="J15" s="28"/>
       <c r="K15" s="27"/>
       <c r="L15" s="27" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19729,16 +19720,16 @@
         <v>21</v>
       </c>
       <c r="D16" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="G16" s="27" t="s">
         <v>423</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>424</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>426</v>
       </c>
       <c r="H16" s="27" t="s">
         <v>25</v>
@@ -19747,7 +19738,7 @@
       <c r="J16" s="28"/>
       <c r="K16" s="27"/>
       <c r="L16" s="27" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19761,10 +19752,10 @@
         <v>21</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F17" s="25" t="s">
         <v>24</v>
@@ -19779,7 +19770,7 @@
       <c r="J17" s="26"/>
       <c r="K17" s="25"/>
       <c r="L17" s="27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19793,16 +19784,16 @@
         <v>21</v>
       </c>
       <c r="D18" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>427</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>428</v>
+      </c>
+      <c r="G18" s="27" t="s">
         <v>429</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>430</v>
-      </c>
-      <c r="F18" s="27" t="s">
-        <v>431</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>432</v>
       </c>
       <c r="H18" s="27" t="s">
         <v>48</v>
@@ -19827,16 +19818,16 @@
         <v>21</v>
       </c>
       <c r="D19" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="G19" s="27" t="s">
         <v>433</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>434</v>
-      </c>
-      <c r="F19" s="27" t="s">
-        <v>435</v>
-      </c>
-      <c r="G19" s="27" t="s">
-        <v>436</v>
       </c>
       <c r="H19" s="27" t="s">
         <v>25</v>
@@ -19859,16 +19850,16 @@
         <v>21</v>
       </c>
       <c r="D20" s="27" t="s">
+        <v>434</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="G20" s="27" t="s">
         <v>437</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>438</v>
-      </c>
-      <c r="F20" s="27" t="s">
-        <v>439</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>440</v>
       </c>
       <c r="H20" s="27" t="s">
         <v>25</v>
@@ -19899,16 +19890,16 @@
         <v>21</v>
       </c>
       <c r="D21" s="27" t="s">
+        <v>438</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>440</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>441</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>442</v>
-      </c>
-      <c r="F21" s="27" t="s">
-        <v>443</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>444</v>
       </c>
       <c r="H21" s="27" t="s">
         <v>25</v>
@@ -19931,16 +19922,16 @@
         <v>21</v>
       </c>
       <c r="D22" s="26" t="s">
+        <v>349</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>350</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>351</v>
+      </c>
+      <c r="G22" s="26" t="s">
         <v>352</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>353</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>355</v>
       </c>
       <c r="H22" s="26" t="s">
         <v>25</v>
@@ -19965,16 +19956,16 @@
         <v>21</v>
       </c>
       <c r="D23" s="57" t="s">
+        <v>302</v>
+      </c>
+      <c r="E23" s="57" t="s">
+        <v>303</v>
+      </c>
+      <c r="F23" s="57" t="s">
+        <v>304</v>
+      </c>
+      <c r="G23" s="57" t="s">
         <v>305</v>
-      </c>
-      <c r="E23" s="57" t="s">
-        <v>306</v>
-      </c>
-      <c r="F23" s="57" t="s">
-        <v>307</v>
-      </c>
-      <c r="G23" s="57" t="s">
-        <v>308</v>
       </c>
       <c r="H23" s="57" t="s">
         <v>25</v>
@@ -20020,7 +20011,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>5</v>
@@ -20070,7 +20061,7 @@
         <v>22</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>24</v>
@@ -20089,7 +20080,7 @@
       </c>
       <c r="K2" s="25"/>
       <c r="L2" s="62" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -20103,16 +20094,16 @@
         <v>21</v>
       </c>
       <c r="D3" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>203</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>205</v>
       </c>
       <c r="H3" s="26" t="s">
         <v>25</v>
@@ -20135,10 +20126,10 @@
         <v>21</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>24</v>
@@ -20153,7 +20144,7 @@
       <c r="J4" s="26"/>
       <c r="K4" s="25"/>
       <c r="L4" s="62" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -20167,16 +20158,16 @@
         <v>21</v>
       </c>
       <c r="D5" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="G5" s="26" t="s">
         <v>209</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>211</v>
       </c>
       <c r="H5" s="26" t="s">
         <v>48</v>
@@ -20188,10 +20179,10 @@
         <v>54</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L5" s="62" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -20205,16 +20196,16 @@
         <v>21</v>
       </c>
       <c r="D6" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="G6" s="26" t="s">
         <v>215</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>217</v>
       </c>
       <c r="H6" s="26" t="s">
         <v>48</v>
@@ -20226,10 +20217,10 @@
         <v>47</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L6" s="62" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -20277,16 +20268,16 @@
         <v>21</v>
       </c>
       <c r="D8" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="G8" s="26" t="s">
         <v>221</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>223</v>
       </c>
       <c r="H8" s="26" t="s">
         <v>25</v>
@@ -20309,16 +20300,16 @@
         <v>21</v>
       </c>
       <c r="D9" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="F9" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="G9" s="26" t="s">
         <v>225</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>227</v>
       </c>
       <c r="H9" s="26" t="s">
         <v>25</v>
@@ -20341,16 +20332,16 @@
         <v>21</v>
       </c>
       <c r="D10" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="F10" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="G10" s="26" t="s">
         <v>229</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>231</v>
       </c>
       <c r="H10" s="26" t="s">
         <v>25</v>
@@ -20373,16 +20364,16 @@
         <v>21</v>
       </c>
       <c r="D11" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="F11" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="G11" s="26" t="s">
         <v>233</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>235</v>
       </c>
       <c r="H11" s="26" t="s">
         <v>25</v>
@@ -20405,16 +20396,16 @@
         <v>21</v>
       </c>
       <c r="D12" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="G12" s="26" t="s">
         <v>237</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>239</v>
       </c>
       <c r="H12" s="26" t="s">
         <v>25</v>
@@ -20437,10 +20428,10 @@
         <v>21</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>24</v>
@@ -20457,7 +20448,7 @@
       </c>
       <c r="K13" s="25"/>
       <c r="L13" s="62" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -20471,16 +20462,16 @@
         <v>21</v>
       </c>
       <c r="D14" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="G14" s="26" t="s">
         <v>243</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>245</v>
       </c>
       <c r="H14" s="26" t="s">
         <v>129</v>
@@ -20492,10 +20483,10 @@
         <v>47</v>
       </c>
       <c r="K14" s="25" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L14" s="62" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -20509,16 +20500,16 @@
         <v>21</v>
       </c>
       <c r="D15" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="G15" s="26" t="s">
         <v>249</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>251</v>
       </c>
       <c r="H15" s="26" t="s">
         <v>25</v>
@@ -20541,16 +20532,16 @@
         <v>21</v>
       </c>
       <c r="D16" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="G16" s="26" t="s">
         <v>253</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>255</v>
       </c>
       <c r="H16" s="26" t="s">
         <v>25</v>
@@ -20573,10 +20564,10 @@
         <v>21</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>24</v>
@@ -20593,7 +20584,7 @@
       </c>
       <c r="K17" s="25"/>
       <c r="L17" s="62" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M17" s="63"/>
       <c r="N17" s="63"/>
@@ -20981,7 +20972,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>5</v>
@@ -21034,7 +21025,7 @@
         <v>22</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>24</v>
@@ -21052,7 +21043,7 @@
       <c r="K2" s="26"/>
       <c r="L2" s="25"/>
       <c r="M2" s="27" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -21066,16 +21057,16 @@
         <v>21</v>
       </c>
       <c r="D3" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="F3" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>261</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>263</v>
       </c>
       <c r="H3" s="26" t="s">
         <v>25</v>
@@ -21101,16 +21092,16 @@
         <v>21</v>
       </c>
       <c r="D4" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>265</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>267</v>
       </c>
       <c r="H4" s="26" t="s">
         <v>25</v>
@@ -21136,16 +21127,16 @@
         <v>21</v>
       </c>
       <c r="D5" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="G5" s="26" t="s">
         <v>269</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>271</v>
       </c>
       <c r="H5" s="26" t="s">
         <v>25</v>
@@ -21171,16 +21162,16 @@
         <v>21</v>
       </c>
       <c r="D6" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="F6" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="G6" s="26" t="s">
         <v>273</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>275</v>
       </c>
       <c r="H6" s="26" t="s">
         <v>25</v>
@@ -21206,16 +21197,16 @@
         <v>21</v>
       </c>
       <c r="D7" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="F7" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="G7" s="26" t="s">
         <v>277</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>279</v>
       </c>
       <c r="H7" s="26" t="s">
         <v>25</v>
@@ -21241,16 +21232,16 @@
         <v>21</v>
       </c>
       <c r="D8" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="F8" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="G8" s="26" t="s">
         <v>281</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>283</v>
       </c>
       <c r="H8" s="26" t="s">
         <v>25</v>
@@ -21276,16 +21267,16 @@
         <v>21</v>
       </c>
       <c r="D9" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="F9" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="G9" s="26" t="s">
         <v>285</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>287</v>
       </c>
       <c r="H9" s="26" t="s">
         <v>25</v>
@@ -21311,16 +21302,16 @@
         <v>21</v>
       </c>
       <c r="D10" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="F10" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="G10" s="26" t="s">
         <v>289</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>291</v>
       </c>
       <c r="H10" s="26" t="s">
         <v>25</v>
@@ -21346,16 +21337,16 @@
         <v>21</v>
       </c>
       <c r="D11" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="F11" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="G11" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>295</v>
       </c>
       <c r="H11" s="26" t="s">
         <v>25</v>
@@ -21369,7 +21360,7 @@
       </c>
       <c r="L11" s="25"/>
       <c r="M11" s="27" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -21383,16 +21374,16 @@
         <v>21</v>
       </c>
       <c r="D12" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="F12" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="G12" s="26" t="s">
         <v>298</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>300</v>
       </c>
       <c r="H12" s="26" t="s">
         <v>129</v>
@@ -21408,7 +21399,7 @@
       </c>
       <c r="L12" s="25"/>
       <c r="M12" s="27" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -21422,16 +21413,16 @@
         <v>21</v>
       </c>
       <c r="D13" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G13" s="26" t="s">
         <v>312</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>315</v>
       </c>
       <c r="H13" s="26" t="s">
         <v>25</v>
@@ -21457,16 +21448,16 @@
         <v>21</v>
       </c>
       <c r="D14" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="G14" s="26" t="s">
         <v>317</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>320</v>
       </c>
       <c r="H14" s="26" t="s">
         <v>25</v>
@@ -21492,16 +21483,16 @@
         <v>21</v>
       </c>
       <c r="D15" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="G15" s="26" t="s">
         <v>321</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>324</v>
       </c>
       <c r="H15" s="26" t="s">
         <v>25</v>
@@ -21515,7 +21506,7 @@
       </c>
       <c r="L15" s="25"/>
       <c r="M15" s="27" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
@@ -21529,16 +21520,16 @@
         <v>21</v>
       </c>
       <c r="D16" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="E16" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>328</v>
-      </c>
       <c r="G16" s="26" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H16" s="26" t="s">
         <v>25</v>
@@ -21564,16 +21555,16 @@
         <v>21</v>
       </c>
       <c r="D17" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="G17" s="26" t="s">
         <v>330</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>333</v>
       </c>
       <c r="H17" s="26" t="s">
         <v>48</v>
@@ -21589,7 +21580,7 @@
       </c>
       <c r="L17" s="25"/>
       <c r="M17" s="27" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
@@ -21603,16 +21594,16 @@
         <v>21</v>
       </c>
       <c r="D18" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="G18" s="26" t="s">
         <v>335</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>338</v>
       </c>
       <c r="H18" s="26" t="s">
         <v>48</v>
@@ -21640,16 +21631,16 @@
         <v>21</v>
       </c>
       <c r="D19" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>338</v>
+      </c>
+      <c r="G19" s="26" t="s">
         <v>339</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>341</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>342</v>
       </c>
       <c r="H19" s="26" t="s">
         <v>25</v>
@@ -21663,7 +21654,7 @@
       </c>
       <c r="L19" s="25"/>
       <c r="M19" s="27" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -21677,16 +21668,16 @@
         <v>21</v>
       </c>
       <c r="D20" s="26" t="s">
+        <v>341</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>343</v>
+      </c>
+      <c r="G20" s="26" t="s">
         <v>344</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>345</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>347</v>
       </c>
       <c r="H20" s="26" t="s">
         <v>25</v>
@@ -21712,16 +21703,16 @@
         <v>21</v>
       </c>
       <c r="D21" s="26" t="s">
+        <v>345</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="G21" s="26" t="s">
         <v>348</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>350</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>351</v>
       </c>
       <c r="H21" s="26" t="s">
         <v>25</v>
@@ -21747,16 +21738,16 @@
         <v>21</v>
       </c>
       <c r="D22" s="26" t="s">
+        <v>354</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="G22" s="26" t="s">
         <v>357</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>358</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>359</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>360</v>
       </c>
       <c r="H22" s="26" t="s">
         <v>25</v>
@@ -21789,7 +21780,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N999"/>
+  <dimension ref="A1:N997"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.83203125" customWidth="1"/>
@@ -21920,7 +21911,7 @@
         <v>47</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N3" s="10" t="s">
         <v>166</v>
@@ -21964,7 +21955,7 @@
         <v>47</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>174</v>
@@ -22008,7 +21999,7 @@
         <v>47</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="N5" s="10" t="s">
         <v>174</v>
@@ -22053,7 +22044,7 @@
       </c>
       <c r="M6" s="9"/>
       <c r="N6" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22091,7 +22082,7 @@
       <c r="L7" s="9"/>
       <c r="M7" s="6"/>
       <c r="N7" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22121,17 +22112,17 @@
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>141</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M8" s="6"/>
       <c r="N8" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22171,7 +22162,7 @@
       </c>
       <c r="M9" s="6"/>
       <c r="N9" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22207,11 +22198,11 @@
         <v>147</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M10" s="6"/>
       <c r="N10" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22241,17 +22232,17 @@
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>138</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M11" s="6"/>
       <c r="N11" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22287,11 +22278,11 @@
         <v>138</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M12" s="6"/>
       <c r="N12" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -22327,11 +22318,11 @@
         <v>141</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M13" s="6"/>
       <c r="N13" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -22366,7 +22357,7 @@
         <v>25</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>54</v>
@@ -22376,7 +22367,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>2</v>
@@ -22385,16 +22376,16 @@
         <v>29</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E15" s="5">
-        <v>1019603840</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>24</v>
+        <v>1024487494</v>
+      </c>
+      <c r="F15" s="7">
+        <v>3043184948</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>25</v>
@@ -22404,17 +22395,17 @@
         <v>25</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>301</v>
+        <v>47</v>
       </c>
       <c r="M15" s="6"/>
       <c r="N15" s="10"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>2</v>
@@ -22423,16 +22414,16 @@
         <v>29</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E16" s="5">
-        <v>1024487494</v>
+        <v>1023895751</v>
       </c>
       <c r="F16" s="7">
-        <v>3043184948</v>
+        <v>3216378582</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>25</v>
@@ -22442,7 +22433,7 @@
         <v>25</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>47</v>
@@ -22452,7 +22443,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>2</v>
@@ -22461,16 +22452,16 @@
         <v>29</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E17" s="5">
-        <v>1023895751</v>
+        <v>1023376503</v>
       </c>
       <c r="F17" s="7">
-        <v>3216378582</v>
+        <v>3212238950</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>25</v>
@@ -22480,7 +22471,7 @@
         <v>25</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>47</v>
@@ -22490,7 +22481,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>2</v>
@@ -22499,16 +22490,16 @@
         <v>29</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E18" s="5">
-        <v>1001067429</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>24</v>
+        <v>1123563667</v>
+      </c>
+      <c r="F18" s="7">
+        <v>3054761708</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>25</v>
@@ -22518,17 +22509,17 @@
         <v>25</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>301</v>
+        <v>54</v>
       </c>
       <c r="M18" s="6"/>
       <c r="N18" s="10"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>2</v>
@@ -22537,16 +22528,16 @@
         <v>29</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E19" s="5">
-        <v>1023376503</v>
+        <v>1073380709</v>
       </c>
       <c r="F19" s="7">
-        <v>3212238950</v>
+        <v>3117742497</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>25</v>
@@ -22556,105 +22547,73 @@
         <v>25</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="10"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
-        <v>20</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>353</v>
+      </c>
+      <c r="C20" s="6"/>
       <c r="D20" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E20" s="5">
-        <v>1123563667</v>
-      </c>
-      <c r="F20" s="7">
-        <v>3054761708</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>25</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77">
+        <v>3122551652</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
       <c r="I20" s="6"/>
-      <c r="J20" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>334</v>
-      </c>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
       <c r="L20" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M20" s="6"/>
-      <c r="N20" s="10"/>
+      <c r="N20" s="6"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
-        <v>21</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B21" s="75"/>
+      <c r="C21" s="6"/>
       <c r="D21" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1073380709</v>
-      </c>
-      <c r="F21" s="7">
-        <v>3117742497</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>25</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="E21" s="78"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
       <c r="I21" s="6"/>
-      <c r="J21" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>334</v>
-      </c>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
       <c r="L21" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M21" s="6"/>
-      <c r="N21" s="10"/>
+      <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
-        <v>22</v>
-      </c>
-      <c r="B22" s="66" t="s">
-        <v>356</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B22" s="75"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69">
-        <v>3122551652</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="E22" s="78"/>
+      <c r="F22" s="78"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
@@ -22668,15 +22627,15 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
-        <v>23</v>
-      </c>
-      <c r="B23" s="67"/>
+        <v>25</v>
+      </c>
+      <c r="B23" s="75"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
+        <v>367</v>
+      </c>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
@@ -22690,15 +22649,15 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
-        <v>24</v>
-      </c>
-      <c r="B24" s="67"/>
+        <v>26</v>
+      </c>
+      <c r="B24" s="75"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="E24" s="70"/>
-      <c r="F24" s="70"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="78"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -22712,15 +22671,15 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
-        <v>25</v>
-      </c>
-      <c r="B25" s="67"/>
+        <v>27</v>
+      </c>
+      <c r="B25" s="75"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
+        <v>374</v>
+      </c>
+      <c r="E25" s="78"/>
+      <c r="F25" s="78"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
@@ -22734,15 +22693,15 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
-        <v>26</v>
-      </c>
-      <c r="B26" s="67"/>
+        <v>28</v>
+      </c>
+      <c r="B26" s="75"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
+        <v>376</v>
+      </c>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -22756,15 +22715,15 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
-        <v>27</v>
-      </c>
-      <c r="B27" s="67"/>
+        <v>29</v>
+      </c>
+      <c r="B27" s="75"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
+        <v>381</v>
+      </c>
+      <c r="E27" s="78"/>
+      <c r="F27" s="78"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
@@ -22778,15 +22737,15 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
-        <v>28</v>
-      </c>
-      <c r="B28" s="67"/>
+        <v>30</v>
+      </c>
+      <c r="B28" s="75"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
+        <v>383</v>
+      </c>
+      <c r="E28" s="78"/>
+      <c r="F28" s="78"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -22800,15 +22759,15 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
-        <v>29</v>
-      </c>
-      <c r="B29" s="67"/>
+        <v>31</v>
+      </c>
+      <c r="B29" s="75"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
+        <v>388</v>
+      </c>
+      <c r="E29" s="78"/>
+      <c r="F29" s="78"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
@@ -22822,15 +22781,15 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
-        <v>30</v>
-      </c>
-      <c r="B30" s="67"/>
+        <v>32</v>
+      </c>
+      <c r="B30" s="76"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
+        <v>390</v>
+      </c>
+      <c r="E30" s="79"/>
+      <c r="F30" s="79"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
@@ -22843,48 +22802,10 @@
       <c r="N30" s="6"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="5">
-        <v>31</v>
-      </c>
-      <c r="B31" s="67"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
+      <c r="F31" s="14"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="5">
-        <v>32</v>
-      </c>
-      <c r="B32" s="68"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
+      <c r="F32" s="14"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F33" s="14"/>
@@ -25781,17 +25702,11 @@
     <row r="997" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F997" s="14"/>
     </row>
-    <row r="998" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F998" s="14"/>
-    </row>
-    <row r="999" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F999" s="14"/>
-    </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B22:B32"/>
-    <mergeCell ref="E22:E32"/>
-    <mergeCell ref="F22:F32"/>
+    <mergeCell ref="B20:B30"/>
+    <mergeCell ref="E20:E30"/>
+    <mergeCell ref="F20:F30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases/Confirmados Asamblea Rural 24 Oct.xlsx
+++ b/Bases/Confirmados Asamblea Rural 24 Oct.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dannamoralesbeltran/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BF9180-7771-6648-A0E8-9821071EF554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD357870-6B2D-6441-B20F-2F0FCCAE2C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17020" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consolidado" sheetId="5" state="hidden" r:id="rId1"/>
@@ -1798,7 +1798,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1989,9 +1989,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2015,6 +2012,19 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3282,6 +3292,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_2" displayName="Tabla_2" ref="A1:M18" headerRowDxfId="18" dataDxfId="16" totalsRowDxfId="14" headerRowBorderDxfId="17" tableBorderDxfId="15">
+  <autoFilter ref="A1:M18" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="N.°" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Punto" dataDxfId="12"/>
@@ -12165,7 +12176,7 @@
     </row>
     <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="17">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>0</v>
@@ -12198,7 +12209,7 @@
     </row>
     <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>0</v>
@@ -12210,16 +12221,16 @@
         <v>21</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F5" s="21">
-        <v>1028485165</v>
+        <v>1027525934</v>
       </c>
       <c r="G5" s="21">
-        <v>3238118237</v>
+        <v>3228421675</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I5" s="18" t="s">
         <v>25</v>
@@ -12228,12 +12239,12 @@
       <c r="K5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="18"/>
-      <c r="M5" s="19"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="82"/>
     </row>
     <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>0</v>
@@ -12245,16 +12256,16 @@
         <v>21</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F6" s="21">
-        <v>1027525934</v>
+        <v>1010247983</v>
       </c>
       <c r="G6" s="21">
-        <v>3228421675</v>
+        <v>3023825243</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I6" s="18" t="s">
         <v>25</v>
@@ -12268,7 +12279,7 @@
     </row>
     <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>0</v>
@@ -12280,16 +12291,16 @@
         <v>21</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F7" s="21">
-        <v>1010247983</v>
+        <v>1071629220</v>
       </c>
       <c r="G7" s="21">
-        <v>3023825243</v>
+        <v>3208685770</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I7" s="18" t="s">
         <v>25</v>
@@ -12303,38 +12314,36 @@
     </row>
     <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="21">
-        <v>1071629220</v>
+      <c r="C8" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="F8" s="22">
+        <v>1006877782</v>
       </c>
       <c r="G8" s="21">
-        <v>3208685770</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="18"/>
+        <v>3193342504</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
       <c r="K8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="18"/>
-      <c r="M8" s="19"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="17">
@@ -12350,10 +12359,10 @@
         <v>447</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F9" s="22">
-        <v>1006877782</v>
+        <v>1022941390</v>
       </c>
       <c r="G9" s="21">
         <v>3193342504</v>
@@ -12371,7 +12380,7 @@
     </row>
     <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>0</v>
@@ -12383,28 +12392,32 @@
         <v>447</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>461</v>
-      </c>
-      <c r="F10" s="22">
-        <v>1022941390</v>
-      </c>
-      <c r="G10" s="21">
-        <v>3193342504</v>
-      </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
+        <v>91</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="J10" s="17"/>
       <c r="K10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17" t="s">
-        <v>458</v>
-      </c>
+      <c r="M10" s="83"/>
     </row>
     <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>0</v>
@@ -12439,7 +12452,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>0</v>
@@ -12464,11 +12477,11 @@
         <v>464</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="70">
-        <v>10</v>
-      </c>
-      <c r="B13" s="18" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="17">
+        <v>12</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="17" t="s">
@@ -12478,30 +12491,24 @@
         <v>447</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="F13" s="22">
-        <v>1028783625</v>
-      </c>
-      <c r="G13" s="21">
-        <v>3193342504</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="F13" s="22"/>
+      <c r="G13" s="21"/>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
-      <c r="K13" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="K13" s="10"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="66">
-        <v>15</v>
-      </c>
-      <c r="B14" s="17" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="17">
+        <v>13</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="17" t="s">
@@ -12511,22 +12518,28 @@
         <v>447</v>
       </c>
       <c r="E14" s="66" t="s">
-        <v>463</v>
-      </c>
-      <c r="F14" s="67"/>
-      <c r="G14" s="68"/>
+        <v>460</v>
+      </c>
+      <c r="F14" s="67">
+        <v>1028783625</v>
+      </c>
+      <c r="G14" s="68">
+        <v>3193342504</v>
+      </c>
       <c r="H14" s="66"/>
       <c r="I14" s="66"/>
       <c r="J14" s="66"/>
-      <c r="K14" s="69"/>
+      <c r="K14" s="69" t="s">
+        <v>47</v>
+      </c>
       <c r="L14" s="66"/>
       <c r="M14" s="17" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="66">
-        <v>12</v>
+      <c r="A15" s="17">
+        <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>0</v>
@@ -12537,31 +12550,23 @@
       <c r="D15" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="E15" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" s="72">
-        <v>1140917549</v>
-      </c>
-      <c r="G15" s="68">
-        <v>3235104254</v>
-      </c>
-      <c r="H15" s="71" t="s">
-        <v>119</v>
-      </c>
-      <c r="I15" s="71" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="71"/>
-      <c r="K15" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="L15" s="72"/>
-      <c r="M15" s="73"/>
-    </row>
-    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="66">
-        <v>13</v>
+      <c r="E15" s="66" t="s">
+        <v>463</v>
+      </c>
+      <c r="F15" s="67"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="17">
+        <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>0</v>
@@ -12572,28 +12577,30 @@
       <c r="D16" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="E16" s="66" t="s">
-        <v>448</v>
-      </c>
-      <c r="F16" s="67">
-        <v>1023031689</v>
-      </c>
-      <c r="G16" s="68" t="s">
-        <v>449</v>
-      </c>
-      <c r="H16" s="66" t="s">
-        <v>450</v>
-      </c>
-      <c r="I16" s="66"/>
-      <c r="J16" s="66"/>
-      <c r="K16" s="72" t="s">
+      <c r="E16" s="70" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="71">
+        <v>1140917549</v>
+      </c>
+      <c r="G16" s="68">
+        <v>3235104254</v>
+      </c>
+      <c r="H16" s="70" t="s">
+        <v>119</v>
+      </c>
+      <c r="I16" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="70"/>
+      <c r="K16" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="L16" s="66"/>
-      <c r="M16" s="66"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="66">
+      <c r="L16" s="71"/>
+      <c r="M16" s="72"/>
+    </row>
+    <row r="17" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="17">
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
@@ -12606,18 +12613,24 @@
         <v>447</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>179</v>
-      </c>
-      <c r="F17" s="67"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="66"/>
+        <v>448</v>
+      </c>
+      <c r="F17" s="67">
+        <v>1023031689</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>449</v>
+      </c>
+      <c r="H17" s="66" t="s">
+        <v>450</v>
+      </c>
       <c r="I17" s="66"/>
       <c r="J17" s="66"/>
-      <c r="K17" s="69"/>
+      <c r="K17" s="71" t="s">
+        <v>47</v>
+      </c>
       <c r="L17" s="66"/>
-      <c r="M17" s="17" t="s">
-        <v>464</v>
-      </c>
+      <c r="M17" s="17"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F18" s="23"/>
@@ -15570,7 +15583,7 @@
     <dataValidation type="list" allowBlank="1" sqref="K12:K13" xr:uid="{8910634A-0E32-2F49-8B09-DCE58B143658}">
       <formula1>"Confirma,Va por su cuenta,No asiste,No contesta,Número equivocado,No puede llegar a la parada,Sin info de contacto"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K11" xr:uid="{E25F0F93-D649-0144-938C-6D58A347FBC8}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K4 K6:K11 L5" xr:uid="{E25F0F93-D649-0144-938C-6D58A347FBC8}">
       <formula1>"Confirma,Va por su cuenta,No asiste,No contesta,Número equivocado,No puede llegar a la parada"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15586,7 +15599,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N994"/>
+  <dimension ref="A1:N993"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
@@ -16220,26 +16233,23 @@
       <c r="C18" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="H18" s="54" t="s">
+      <c r="D18" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="79">
+        <v>1028485165</v>
+      </c>
+      <c r="F18" s="79">
+        <v>3238118237</v>
+      </c>
+      <c r="G18" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="55" t="s">
+      <c r="I18" s="79"/>
+      <c r="J18" s="55" t="s">
         <v>47</v>
       </c>
       <c r="L18" s="54"/>
@@ -19159,7 +19169,7 @@
     <row r="989" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E989" s="23"/>
     </row>
-    <row r="990" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="990" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E990" s="23"/>
     </row>
     <row r="991" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -19171,12 +19181,9 @@
     <row r="993" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E993" s="23"/>
     </row>
-    <row r="994" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E994" s="23"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K18" xr:uid="{00000000-0002-0000-0800-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J18 K2:K17" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>"Confirma,Va por su cuenta,No asiste,No contesta,Número equivocado,No puede llegar a la parada"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22559,15 +22566,15 @@
       <c r="A20" s="5">
         <v>22</v>
       </c>
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="73" t="s">
         <v>353</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77">
+      <c r="E20" s="76"/>
+      <c r="F20" s="76">
         <v>3122551652</v>
       </c>
       <c r="G20" s="6"/>
@@ -22585,13 +22592,13 @@
       <c r="A21" s="5">
         <v>23</v>
       </c>
-      <c r="B21" s="75"/>
+      <c r="B21" s="74"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
@@ -22607,13 +22614,13 @@
       <c r="A22" s="5">
         <v>24</v>
       </c>
-      <c r="B22" s="75"/>
+      <c r="B22" s="74"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
@@ -22629,13 +22636,13 @@
       <c r="A23" s="5">
         <v>25</v>
       </c>
-      <c r="B23" s="75"/>
+      <c r="B23" s="74"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
@@ -22651,13 +22658,13 @@
       <c r="A24" s="5">
         <v>26</v>
       </c>
-      <c r="B24" s="75"/>
+      <c r="B24" s="74"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -22673,13 +22680,13 @@
       <c r="A25" s="5">
         <v>27</v>
       </c>
-      <c r="B25" s="75"/>
+      <c r="B25" s="74"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
@@ -22695,13 +22702,13 @@
       <c r="A26" s="5">
         <v>28</v>
       </c>
-      <c r="B26" s="75"/>
+      <c r="B26" s="74"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -22717,13 +22724,13 @@
       <c r="A27" s="5">
         <v>29</v>
       </c>
-      <c r="B27" s="75"/>
+      <c r="B27" s="74"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="77"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
@@ -22739,13 +22746,13 @@
       <c r="A28" s="5">
         <v>30</v>
       </c>
-      <c r="B28" s="75"/>
+      <c r="B28" s="74"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -22761,13 +22768,13 @@
       <c r="A29" s="5">
         <v>31</v>
       </c>
-      <c r="B29" s="75"/>
+      <c r="B29" s="74"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="77"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
@@ -22783,13 +22790,13 @@
       <c r="A30" s="5">
         <v>32</v>
       </c>
-      <c r="B30" s="76"/>
+      <c r="B30" s="75"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="78"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
